--- a/outputs/ToT_tukey_classification_matrix.xlsx
+++ b/outputs/ToT_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="201">
   <si>
     <t>2013 Jan</t>
   </si>
@@ -572,6 +572,9 @@
   </si>
   <si>
     <t>Alarm</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>8%</t>
@@ -1951,13 +1954,13 @@
         <v>183</v>
       </c>
       <c r="FB2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="FC2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="FD2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:160">
@@ -2433,13 +2436,13 @@
         <v>183</v>
       </c>
       <c r="FB3" t="s">
+        <v>188</v>
+      </c>
+      <c r="FC3" t="s">
+        <v>195</v>
+      </c>
+      <c r="FD3" t="s">
         <v>187</v>
-      </c>
-      <c r="FC3" t="s">
-        <v>194</v>
-      </c>
-      <c r="FD3" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:160">
@@ -2732,7 +2735,7 @@
         <v>183</v>
       </c>
       <c r="CS4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CT4" t="s">
         <v>183</v>
@@ -2915,13 +2918,13 @@
         <v>183</v>
       </c>
       <c r="FB4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FC4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FD4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:160">
@@ -3397,13 +3400,13 @@
         <v>183</v>
       </c>
       <c r="FB5" t="s">
+        <v>189</v>
+      </c>
+      <c r="FC5" t="s">
         <v>188</v>
       </c>
-      <c r="FC5" t="s">
-        <v>187</v>
-      </c>
       <c r="FD5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:160">
@@ -3879,13 +3882,13 @@
         <v>183</v>
       </c>
       <c r="FB6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="FC6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="FD6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:160">
@@ -4361,13 +4364,13 @@
         <v>183</v>
       </c>
       <c r="FB7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FC7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FD7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:160">
@@ -4843,13 +4846,13 @@
         <v>183</v>
       </c>
       <c r="FB8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="FC8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="FD8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:160">
@@ -5325,13 +5328,13 @@
         <v>183</v>
       </c>
       <c r="FB9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="FC9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="FD9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:160">
@@ -5807,13 +5810,13 @@
         <v>183</v>
       </c>
       <c r="FB10" t="s">
+        <v>193</v>
+      </c>
+      <c r="FC10" t="s">
         <v>192</v>
       </c>
-      <c r="FC10" t="s">
-        <v>191</v>
-      </c>
       <c r="FD10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:160">
@@ -6289,13 +6292,13 @@
         <v>183</v>
       </c>
       <c r="FB11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="FC11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="FD11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:160">
@@ -6771,13 +6774,13 @@
         <v>183</v>
       </c>
       <c r="FB12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="FC12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="FD12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:160">
@@ -7193,7 +7196,7 @@
         <v>183</v>
       </c>
       <c r="EH13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EI13" t="s">
         <v>183</v>
@@ -7253,13 +7256,13 @@
         <v>183</v>
       </c>
       <c r="FB13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FC13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="FD13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:160">
@@ -7735,13 +7738,13 @@
         <v>183</v>
       </c>
       <c r="FB14" t="s">
+        <v>190</v>
+      </c>
+      <c r="FC14" t="s">
+        <v>190</v>
+      </c>
+      <c r="FD14" t="s">
         <v>189</v>
-      </c>
-      <c r="FC14" t="s">
-        <v>189</v>
-      </c>
-      <c r="FD14" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:160">
@@ -8217,13 +8220,13 @@
         <v>183</v>
       </c>
       <c r="FB15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="FC15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="FD15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:160">
@@ -8699,13 +8702,13 @@
         <v>183</v>
       </c>
       <c r="FB16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="FC16" t="s">
+        <v>190</v>
+      </c>
+      <c r="FD16" t="s">
         <v>189</v>
-      </c>
-      <c r="FD16" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="17" spans="1:160">
@@ -8932,217 +8935,217 @@
         <v>183</v>
       </c>
       <c r="BW17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="BX17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="BY17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="BZ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CA17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CB17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CC17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CD17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CE17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CF17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CG17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CH17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CI17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CJ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CK17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CL17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CM17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CN17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CO17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CP17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CQ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CR17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CS17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CT17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CU17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CV17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CW17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CX17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CY17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CZ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DA17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DB17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DC17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DD17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DE17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DF17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DG17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DH17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DI17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DJ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DK17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DL17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DM17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DN17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DO17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DP17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DQ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DR17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DS17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DT17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DU17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DV17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DW17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DX17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DY17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DZ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EA17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EB17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EC17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="ED17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EE17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EF17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EG17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EH17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EI17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EJ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EK17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EL17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EM17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EN17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EO17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EP17" t="s">
         <v>183</v>
@@ -9181,13 +9184,13 @@
         <v>183</v>
       </c>
       <c r="FB17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="FC17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FD17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:160">
@@ -9663,13 +9666,13 @@
         <v>183</v>
       </c>
       <c r="FB18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FC18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="FD18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:160">
@@ -10145,13 +10148,13 @@
         <v>183</v>
       </c>
       <c r="FB19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="FC19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="FD19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:160">
@@ -10627,13 +10630,13 @@
         <v>183</v>
       </c>
       <c r="FB20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FC20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FD20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:160">
@@ -11109,13 +11112,13 @@
         <v>183</v>
       </c>
       <c r="FB21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="FC21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="FD21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:160">
@@ -11591,13 +11594,13 @@
         <v>183</v>
       </c>
       <c r="FB22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="FC22" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FD22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:160">
@@ -11962,7 +11965,7 @@
         <v>184</v>
       </c>
       <c r="DQ23" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DR23" t="s">
         <v>185</v>
@@ -12073,13 +12076,13 @@
         <v>183</v>
       </c>
       <c r="FB23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="FC23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="FD23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:160">
@@ -12555,13 +12558,13 @@
         <v>183</v>
       </c>
       <c r="FB24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="FC24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FD24" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ToT_tukey_classification_matrix.xlsx
+++ b/outputs/ToT_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="186">
   <si>
     <t>2013 Jan</t>
   </si>
@@ -568,55 +568,10 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>No data</t>
   </si>
   <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>5%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>9%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>13%</t>
   </si>
 </sst>
 </file>
@@ -1636,331 +1591,331 @@
         <v>183</v>
       </c>
       <c r="AZ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY2" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER2" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES2" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY2" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ2" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA2" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB2" t="s">
         <v>185</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="FC2" t="s">
         <v>185</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="FD2" t="s">
         <v>185</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>185</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BX2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BZ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CA2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CB2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY2" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DK2" t="s">
-        <v>184</v>
-      </c>
-      <c r="DL2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DM2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DN2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DO2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DP2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DQ2" t="s">
-        <v>184</v>
-      </c>
-      <c r="DR2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DS2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DT2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DU2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV2" t="s">
-        <v>184</v>
-      </c>
-      <c r="DW2" t="s">
-        <v>185</v>
-      </c>
-      <c r="DX2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY2" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC2" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER2" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES2" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY2" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ2" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA2" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB2" t="s">
-        <v>187</v>
-      </c>
-      <c r="FC2" t="s">
-        <v>193</v>
-      </c>
-      <c r="FD2" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:160">
@@ -2007,7 +1962,7 @@
         <v>183</v>
       </c>
       <c r="O3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P3" t="s">
         <v>183</v>
@@ -2016,7 +1971,7 @@
         <v>183</v>
       </c>
       <c r="R3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="S3" t="s">
         <v>183</v>
@@ -2124,10 +2079,10 @@
         <v>183</v>
       </c>
       <c r="BB3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BC3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BD3" t="s">
         <v>183</v>
@@ -2139,7 +2094,7 @@
         <v>183</v>
       </c>
       <c r="BG3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BH3" t="s">
         <v>183</v>
@@ -2316,10 +2271,10 @@
         <v>183</v>
       </c>
       <c r="DN3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DO3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DP3" t="s">
         <v>183</v>
@@ -2328,121 +2283,121 @@
         <v>183</v>
       </c>
       <c r="DR3" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS3" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT3" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU3" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV3" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW3" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX3" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY3" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC3" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ3" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER3" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES3" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY3" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ3" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA3" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB3" t="s">
         <v>185</v>
       </c>
-      <c r="DS3" t="s">
-        <v>184</v>
-      </c>
-      <c r="DT3" t="s">
+      <c r="FC3" t="s">
         <v>185</v>
       </c>
-      <c r="DU3" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV3" t="s">
-        <v>184</v>
-      </c>
-      <c r="DW3" t="s">
-        <v>184</v>
-      </c>
-      <c r="DX3" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY3" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC3" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ3" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER3" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES3" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY3" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ3" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA3" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB3" t="s">
-        <v>188</v>
-      </c>
-      <c r="FC3" t="s">
-        <v>195</v>
-      </c>
       <c r="FD3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:160">
@@ -2735,7 +2690,7 @@
         <v>183</v>
       </c>
       <c r="CS4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CT4" t="s">
         <v>183</v>
@@ -2795,136 +2750,136 @@
         <v>183</v>
       </c>
       <c r="DM4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DN4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY4" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC4" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ4" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER4" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES4" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ4" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA4" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB4" t="s">
         <v>185</v>
       </c>
-      <c r="DO4" t="s">
-        <v>184</v>
-      </c>
-      <c r="DP4" t="s">
-        <v>183</v>
-      </c>
-      <c r="DQ4" t="s">
-        <v>183</v>
-      </c>
-      <c r="DR4" t="s">
-        <v>183</v>
-      </c>
-      <c r="DS4" t="s">
-        <v>183</v>
-      </c>
-      <c r="DT4" t="s">
-        <v>183</v>
-      </c>
-      <c r="DU4" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV4" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW4" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX4" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY4" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC4" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ4" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER4" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES4" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY4" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ4" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA4" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB4" t="s">
-        <v>188</v>
-      </c>
       <c r="FC4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="FD4" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:160">
@@ -3274,139 +3229,139 @@
         <v>183</v>
       </c>
       <c r="DL5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DM5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY5" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC5" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ5" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER5" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES5" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ5" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA5" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB5" t="s">
         <v>185</v>
       </c>
-      <c r="DN5" t="s">
+      <c r="FC5" t="s">
         <v>185</v>
       </c>
-      <c r="DO5" t="s">
+      <c r="FD5" t="s">
         <v>185</v>
-      </c>
-      <c r="DP5" t="s">
-        <v>185</v>
-      </c>
-      <c r="DQ5" t="s">
-        <v>185</v>
-      </c>
-      <c r="DR5" t="s">
-        <v>185</v>
-      </c>
-      <c r="DS5" t="s">
-        <v>185</v>
-      </c>
-      <c r="DT5" t="s">
-        <v>185</v>
-      </c>
-      <c r="DU5" t="s">
-        <v>184</v>
-      </c>
-      <c r="DV5" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW5" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX5" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY5" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC5" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ5" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER5" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES5" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY5" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ5" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA5" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB5" t="s">
-        <v>189</v>
-      </c>
-      <c r="FC5" t="s">
-        <v>188</v>
-      </c>
-      <c r="FD5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:160">
@@ -3564,331 +3519,331 @@
         <v>183</v>
       </c>
       <c r="AZ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY6" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY6" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC6" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER6" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES6" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY6" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ6" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA6" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB6" t="s">
         <v>185</v>
       </c>
-      <c r="BA6" t="s">
+      <c r="FC6" t="s">
         <v>185</v>
       </c>
-      <c r="BB6" t="s">
-        <v>184</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>184</v>
-      </c>
-      <c r="BF6" t="s">
+      <c r="FD6" t="s">
         <v>185</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>185</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>185</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>183</v>
-      </c>
-      <c r="BZ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CB6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CC6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CD6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CE6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CF6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CG6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY6" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DG6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DK6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DL6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DM6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DN6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DO6" t="s">
-        <v>184</v>
-      </c>
-      <c r="DP6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DQ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DR6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DS6" t="s">
-        <v>184</v>
-      </c>
-      <c r="DT6" t="s">
-        <v>184</v>
-      </c>
-      <c r="DU6" t="s">
-        <v>184</v>
-      </c>
-      <c r="DV6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY6" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC6" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER6" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES6" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY6" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ6" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA6" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB6" t="s">
-        <v>190</v>
-      </c>
-      <c r="FC6" t="s">
-        <v>192</v>
-      </c>
-      <c r="FD6" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:160">
@@ -3944,433 +3899,433 @@
         <v>183</v>
       </c>
       <c r="R7" t="s">
+        <v>183</v>
+      </c>
+      <c r="S7" t="s">
+        <v>183</v>
+      </c>
+      <c r="T7" t="s">
+        <v>183</v>
+      </c>
+      <c r="U7" t="s">
+        <v>183</v>
+      </c>
+      <c r="V7" t="s">
+        <v>183</v>
+      </c>
+      <c r="W7" t="s">
+        <v>183</v>
+      </c>
+      <c r="X7" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>183</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CE7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY7" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY7" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC7" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER7" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES7" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY7" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ7" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA7" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB7" t="s">
         <v>185</v>
       </c>
-      <c r="S7" t="s">
-        <v>183</v>
-      </c>
-      <c r="T7" t="s">
-        <v>183</v>
-      </c>
-      <c r="U7" t="s">
-        <v>183</v>
-      </c>
-      <c r="V7" t="s">
-        <v>183</v>
-      </c>
-      <c r="W7" t="s">
-        <v>183</v>
-      </c>
-      <c r="X7" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>183</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA7" t="s">
+      <c r="FC7" t="s">
         <v>185</v>
       </c>
-      <c r="AB7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>184</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>184</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>183</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BH7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>183</v>
-      </c>
-      <c r="BZ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CA7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CC7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CD7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CE7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CF7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CG7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY7" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DG7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DK7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DL7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DM7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DN7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DO7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DP7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DQ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DR7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DS7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DT7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DU7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY7" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC7" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER7" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES7" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY7" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ7" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA7" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB7" t="s">
-        <v>188</v>
-      </c>
-      <c r="FC7" t="s">
-        <v>188</v>
-      </c>
       <c r="FD7" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:160">
@@ -4537,7 +4492,7 @@
         <v>183</v>
       </c>
       <c r="BC8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BD8" t="s">
         <v>183</v>
@@ -4720,7 +4675,7 @@
         <v>183</v>
       </c>
       <c r="DL8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DM8" t="s">
         <v>183</v>
@@ -4729,7 +4684,7 @@
         <v>183</v>
       </c>
       <c r="DO8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DP8" t="s">
         <v>183</v>
@@ -4744,7 +4699,7 @@
         <v>183</v>
       </c>
       <c r="DT8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DU8" t="s">
         <v>183</v>
@@ -4825,7 +4780,7 @@
         <v>183</v>
       </c>
       <c r="EU8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="EV8" t="s">
         <v>183</v>
@@ -4834,7 +4789,7 @@
         <v>183</v>
       </c>
       <c r="EX8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="EY8" t="s">
         <v>183</v>
@@ -4846,13 +4801,13 @@
         <v>183</v>
       </c>
       <c r="FB8" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="FC8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="FD8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:160">
@@ -5013,328 +4968,328 @@
         <v>183</v>
       </c>
       <c r="BA9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BB9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY9" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY9" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC9" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER9" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES9" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY9" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ9" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA9" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB9" t="s">
         <v>185</v>
       </c>
-      <c r="BC9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>184</v>
-      </c>
-      <c r="BE9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BF9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BG9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BH9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY9" t="s">
+      <c r="FC9" t="s">
         <v>185</v>
       </c>
-      <c r="BZ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CA9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>184</v>
-      </c>
-      <c r="CC9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CD9" t="s">
-        <v>184</v>
-      </c>
-      <c r="CE9" t="s">
+      <c r="FD9" t="s">
         <v>185</v>
-      </c>
-      <c r="CF9" t="s">
-        <v>185</v>
-      </c>
-      <c r="CG9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY9" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF9" t="s">
-        <v>185</v>
-      </c>
-      <c r="DG9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DK9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DL9" t="s">
-        <v>185</v>
-      </c>
-      <c r="DM9" t="s">
-        <v>184</v>
-      </c>
-      <c r="DN9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DO9" t="s">
-        <v>184</v>
-      </c>
-      <c r="DP9" t="s">
-        <v>185</v>
-      </c>
-      <c r="DQ9" t="s">
-        <v>184</v>
-      </c>
-      <c r="DR9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DS9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DT9" t="s">
-        <v>184</v>
-      </c>
-      <c r="DU9" t="s">
-        <v>184</v>
-      </c>
-      <c r="DV9" t="s">
-        <v>184</v>
-      </c>
-      <c r="DW9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY9" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC9" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER9" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES9" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY9" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ9" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA9" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB9" t="s">
-        <v>192</v>
-      </c>
-      <c r="FC9" t="s">
-        <v>195</v>
-      </c>
-      <c r="FD9" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:160">
@@ -5495,328 +5450,328 @@
         <v>183</v>
       </c>
       <c r="BA10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BB10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BX10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BY10" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CD10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CE10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY10" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY10" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC10" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER10" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES10" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY10" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ10" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA10" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB10" t="s">
         <v>185</v>
       </c>
-      <c r="BC10" t="s">
+      <c r="FC10" t="s">
         <v>185</v>
       </c>
-      <c r="BD10" t="s">
-        <v>184</v>
-      </c>
-      <c r="BE10" t="s">
-        <v>184</v>
-      </c>
-      <c r="BF10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BG10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BH10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BX10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY10" t="s">
-        <v>183</v>
-      </c>
-      <c r="BZ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CA10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CC10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CD10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CE10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CF10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CG10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY10" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DG10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DK10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DL10" t="s">
+      <c r="FD10" t="s">
         <v>185</v>
-      </c>
-      <c r="DM10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DN10" t="s">
-        <v>184</v>
-      </c>
-      <c r="DO10" t="s">
-        <v>184</v>
-      </c>
-      <c r="DP10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DQ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DR10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DS10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DT10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DU10" t="s">
-        <v>184</v>
-      </c>
-      <c r="DV10" t="s">
-        <v>184</v>
-      </c>
-      <c r="DW10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY10" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC10" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER10" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES10" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY10" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ10" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA10" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB10" t="s">
-        <v>193</v>
-      </c>
-      <c r="FC10" t="s">
-        <v>192</v>
-      </c>
-      <c r="FD10" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:160">
@@ -6292,13 +6247,13 @@
         <v>183</v>
       </c>
       <c r="FB11" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="FC11" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="FD11" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:160">
@@ -6648,7 +6603,7 @@
         <v>183</v>
       </c>
       <c r="DL12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DM12" t="s">
         <v>183</v>
@@ -6660,7 +6615,7 @@
         <v>183</v>
       </c>
       <c r="DP12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DQ12" t="s">
         <v>183</v>
@@ -6672,7 +6627,7 @@
         <v>183</v>
       </c>
       <c r="DT12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DU12" t="s">
         <v>183</v>
@@ -6774,13 +6729,13 @@
         <v>183</v>
       </c>
       <c r="FB12" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="FC12" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="FD12" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:160">
@@ -7031,238 +6986,238 @@
         <v>183</v>
       </c>
       <c r="CE13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY13" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY13" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC13" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH13" t="s">
         <v>184</v>
       </c>
-      <c r="CF13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CG13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY13" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DG13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DK13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DL13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DM13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DN13" t="s">
-        <v>184</v>
-      </c>
-      <c r="DO13" t="s">
-        <v>184</v>
-      </c>
-      <c r="DP13" t="s">
-        <v>184</v>
-      </c>
-      <c r="DQ13" t="s">
-        <v>184</v>
-      </c>
-      <c r="DR13" t="s">
-        <v>184</v>
-      </c>
-      <c r="DS13" t="s">
+      <c r="EI13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ13" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER13" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES13" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY13" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ13" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA13" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB13" t="s">
         <v>185</v>
       </c>
-      <c r="DT13" t="s">
-        <v>184</v>
-      </c>
-      <c r="DU13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY13" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC13" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH13" t="s">
-        <v>186</v>
-      </c>
-      <c r="EI13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ13" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER13" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES13" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY13" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ13" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA13" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB13" t="s">
-        <v>188</v>
-      </c>
       <c r="FC13" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="FD13" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:160">
@@ -7597,7 +7552,7 @@
         <v>183</v>
       </c>
       <c r="DG14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DH14" t="s">
         <v>183</v>
@@ -7618,133 +7573,133 @@
         <v>183</v>
       </c>
       <c r="DN14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DO14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DP14" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ14" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR14" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS14" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT14" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU14" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV14" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW14" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX14" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY14" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC14" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ14" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER14" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES14" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY14" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ14" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA14" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB14" t="s">
         <v>185</v>
       </c>
-      <c r="DQ14" t="s">
-        <v>184</v>
-      </c>
-      <c r="DR14" t="s">
+      <c r="FC14" t="s">
         <v>185</v>
       </c>
-      <c r="DS14" t="s">
+      <c r="FD14" t="s">
         <v>185</v>
-      </c>
-      <c r="DT14" t="s">
-        <v>185</v>
-      </c>
-      <c r="DU14" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV14" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW14" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX14" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY14" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC14" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ14" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER14" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES14" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY14" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ14" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA14" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB14" t="s">
-        <v>190</v>
-      </c>
-      <c r="FC14" t="s">
-        <v>190</v>
-      </c>
-      <c r="FD14" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:160">
@@ -7905,328 +7860,328 @@
         <v>183</v>
       </c>
       <c r="BA15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BB15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BX15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BY15" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CD15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CE15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY15" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY15" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC15" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER15" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES15" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY15" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ15" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA15" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB15" t="s">
         <v>185</v>
       </c>
-      <c r="BC15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BD15" t="s">
-        <v>184</v>
-      </c>
-      <c r="BE15" t="s">
+      <c r="FC15" t="s">
         <v>185</v>
       </c>
-      <c r="BF15" t="s">
+      <c r="FD15" t="s">
         <v>185</v>
-      </c>
-      <c r="BG15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BH15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BX15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY15" t="s">
-        <v>183</v>
-      </c>
-      <c r="BZ15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CA15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CC15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CD15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CE15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CF15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CG15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY15" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DG15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ15" t="s">
-        <v>184</v>
-      </c>
-      <c r="DK15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DL15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DM15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DN15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DO15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DP15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DQ15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DR15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DS15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DT15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DU15" t="s">
-        <v>185</v>
-      </c>
-      <c r="DV15" t="s">
-        <v>184</v>
-      </c>
-      <c r="DW15" t="s">
-        <v>184</v>
-      </c>
-      <c r="DX15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY15" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC15" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ15" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER15" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES15" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY15" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ15" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA15" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB15" t="s">
-        <v>194</v>
-      </c>
-      <c r="FC15" t="s">
-        <v>190</v>
-      </c>
-      <c r="FD15" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:160">
@@ -8387,328 +8342,328 @@
         <v>183</v>
       </c>
       <c r="BA16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BB16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BX16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BY16" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CD16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CE16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY16" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY16" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC16" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER16" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES16" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY16" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ16" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA16" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB16" t="s">
         <v>185</v>
       </c>
-      <c r="BB16" t="s">
-        <v>184</v>
-      </c>
-      <c r="BC16" t="s">
+      <c r="FC16" t="s">
         <v>185</v>
       </c>
-      <c r="BD16" t="s">
+      <c r="FD16" t="s">
         <v>185</v>
-      </c>
-      <c r="BE16" t="s">
-        <v>184</v>
-      </c>
-      <c r="BF16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BG16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BH16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BX16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY16" t="s">
-        <v>183</v>
-      </c>
-      <c r="BZ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CA16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CC16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CD16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CE16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CF16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CG16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY16" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DG16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DK16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DL16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DM16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DN16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DO16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DP16" t="s">
-        <v>184</v>
-      </c>
-      <c r="DQ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DR16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DS16" t="s">
-        <v>184</v>
-      </c>
-      <c r="DT16" t="s">
-        <v>184</v>
-      </c>
-      <c r="DU16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY16" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC16" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER16" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES16" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY16" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ16" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA16" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB16" t="s">
-        <v>193</v>
-      </c>
-      <c r="FC16" t="s">
-        <v>190</v>
-      </c>
-      <c r="FD16" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:160">
@@ -8875,277 +8830,277 @@
         <v>183</v>
       </c>
       <c r="BC17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV17" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW17" t="s">
         <v>184</v>
       </c>
-      <c r="BD17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BE17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BF17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BG17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BH17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV17" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW17" t="s">
-        <v>186</v>
-      </c>
       <c r="BX17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BY17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BZ17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CA17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CB17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CC17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CD17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CE17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CF17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CG17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CH17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CI17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CJ17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CK17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CL17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CM17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CN17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CO17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CP17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CQ17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CR17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CS17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CT17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CU17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CV17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CW17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CX17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CY17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="CZ17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DA17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DB17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DC17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DD17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DE17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DF17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DG17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DH17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DI17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DJ17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DK17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DL17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DM17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DN17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DO17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DP17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DQ17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DR17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DS17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DT17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DU17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DV17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DW17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DX17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DY17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="DZ17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EA17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EB17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EC17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="ED17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EE17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EF17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EG17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EH17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EI17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EJ17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EK17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EL17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EM17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EN17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EO17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="EP17" t="s">
         <v>183</v>
@@ -9184,13 +9139,13 @@
         <v>183</v>
       </c>
       <c r="FB17" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="FC17" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="FD17" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:160">
@@ -9354,7 +9309,7 @@
         <v>183</v>
       </c>
       <c r="BB18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BC18" t="s">
         <v>183</v>
@@ -9540,139 +9495,139 @@
         <v>183</v>
       </c>
       <c r="DL18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY18" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC18" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ18" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER18" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES18" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY18" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ18" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA18" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB18" t="s">
         <v>185</v>
       </c>
-      <c r="DM18" t="s">
-        <v>184</v>
-      </c>
-      <c r="DN18" t="s">
-        <v>183</v>
-      </c>
-      <c r="DO18" t="s">
-        <v>184</v>
-      </c>
-      <c r="DP18" t="s">
-        <v>183</v>
-      </c>
-      <c r="DQ18" t="s">
-        <v>183</v>
-      </c>
-      <c r="DR18" t="s">
-        <v>183</v>
-      </c>
-      <c r="DS18" t="s">
-        <v>184</v>
-      </c>
-      <c r="DT18" t="s">
-        <v>183</v>
-      </c>
-      <c r="DU18" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV18" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW18" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX18" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY18" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC18" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ18" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER18" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES18" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY18" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ18" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA18" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB18" t="s">
-        <v>188</v>
-      </c>
       <c r="FC18" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="FD18" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:160">
@@ -10031,7 +9986,7 @@
         <v>183</v>
       </c>
       <c r="DO19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DP19" t="s">
         <v>183</v>
@@ -10040,13 +9995,13 @@
         <v>183</v>
       </c>
       <c r="DR19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DS19" t="s">
         <v>183</v>
       </c>
       <c r="DT19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="DU19" t="s">
         <v>183</v>
@@ -10148,13 +10103,13 @@
         <v>183</v>
       </c>
       <c r="FB19" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="FC19" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="FD19" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:160">
@@ -10294,349 +10249,349 @@
         <v>183</v>
       </c>
       <c r="AT20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AU20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>183</v>
+      </c>
+      <c r="AZ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BA20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BB20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BX20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BY20" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CD20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CE20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY20" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY20" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC20" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER20" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES20" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY20" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ20" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA20" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB20" t="s">
         <v>185</v>
       </c>
-      <c r="AV20" t="s">
-        <v>183</v>
-      </c>
-      <c r="AW20" t="s">
-        <v>183</v>
-      </c>
-      <c r="AX20" t="s">
-        <v>183</v>
-      </c>
-      <c r="AY20" t="s">
-        <v>183</v>
-      </c>
-      <c r="AZ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BA20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BB20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BC20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BD20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BE20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BF20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BH20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BX20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY20" t="s">
-        <v>183</v>
-      </c>
-      <c r="BZ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CA20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CB20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CC20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CD20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CE20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CF20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CG20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY20" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DG20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DK20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DL20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DM20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DN20" t="s">
-        <v>184</v>
-      </c>
-      <c r="DO20" t="s">
+      <c r="FC20" t="s">
         <v>185</v>
       </c>
-      <c r="DP20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DQ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DR20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DS20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DT20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DU20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY20" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC20" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER20" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES20" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY20" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ20" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA20" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB20" t="s">
-        <v>188</v>
-      </c>
-      <c r="FC20" t="s">
-        <v>188</v>
-      </c>
       <c r="FD20" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:160">
@@ -10683,7 +10638,7 @@
         <v>183</v>
       </c>
       <c r="O21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P21" t="s">
         <v>183</v>
@@ -10695,7 +10650,7 @@
         <v>183</v>
       </c>
       <c r="S21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="T21" t="s">
         <v>183</v>
@@ -10788,337 +10743,337 @@
         <v>183</v>
       </c>
       <c r="AX21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AY21" t="s">
+        <v>183</v>
+      </c>
+      <c r="AZ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BB21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BX21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BY21" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CD21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CE21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY21" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY21" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC21" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER21" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES21" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY21" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ21" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA21" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB21" t="s">
         <v>185</v>
       </c>
-      <c r="AZ21" t="s">
+      <c r="FC21" t="s">
         <v>185</v>
       </c>
-      <c r="BA21" t="s">
+      <c r="FD21" t="s">
         <v>185</v>
-      </c>
-      <c r="BB21" t="s">
-        <v>185</v>
-      </c>
-      <c r="BC21" t="s">
-        <v>185</v>
-      </c>
-      <c r="BD21" t="s">
-        <v>184</v>
-      </c>
-      <c r="BE21" t="s">
-        <v>184</v>
-      </c>
-      <c r="BF21" t="s">
-        <v>184</v>
-      </c>
-      <c r="BG21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BH21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BX21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY21" t="s">
-        <v>183</v>
-      </c>
-      <c r="BZ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CA21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CC21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CD21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CE21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CF21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CG21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY21" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DG21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DK21" t="s">
-        <v>185</v>
-      </c>
-      <c r="DL21" t="s">
-        <v>185</v>
-      </c>
-      <c r="DM21" t="s">
-        <v>185</v>
-      </c>
-      <c r="DN21" t="s">
-        <v>185</v>
-      </c>
-      <c r="DO21" t="s">
-        <v>185</v>
-      </c>
-      <c r="DP21" t="s">
-        <v>185</v>
-      </c>
-      <c r="DQ21" t="s">
-        <v>185</v>
-      </c>
-      <c r="DR21" t="s">
-        <v>184</v>
-      </c>
-      <c r="DS21" t="s">
-        <v>184</v>
-      </c>
-      <c r="DT21" t="s">
-        <v>184</v>
-      </c>
-      <c r="DU21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY21" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC21" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER21" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES21" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY21" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ21" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA21" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB21" t="s">
-        <v>187</v>
-      </c>
-      <c r="FC21" t="s">
-        <v>195</v>
-      </c>
-      <c r="FD21" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:160">
@@ -11468,139 +11423,139 @@
         <v>183</v>
       </c>
       <c r="DL22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY22" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC22" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ22" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER22" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES22" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY22" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ22" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA22" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB22" t="s">
         <v>185</v>
       </c>
-      <c r="DM22" t="s">
+      <c r="FC22" t="s">
         <v>185</v>
       </c>
-      <c r="DN22" t="s">
+      <c r="FD22" t="s">
         <v>185</v>
-      </c>
-      <c r="DO22" t="s">
-        <v>185</v>
-      </c>
-      <c r="DP22" t="s">
-        <v>185</v>
-      </c>
-      <c r="DQ22" t="s">
-        <v>185</v>
-      </c>
-      <c r="DR22" t="s">
-        <v>185</v>
-      </c>
-      <c r="DS22" t="s">
-        <v>185</v>
-      </c>
-      <c r="DT22" t="s">
-        <v>185</v>
-      </c>
-      <c r="DU22" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV22" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW22" t="s">
-        <v>184</v>
-      </c>
-      <c r="DX22" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY22" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC22" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ22" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER22" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES22" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY22" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ22" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA22" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB22" t="s">
-        <v>195</v>
-      </c>
-      <c r="FC22" t="s">
-        <v>188</v>
-      </c>
-      <c r="FD22" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:160">
@@ -11947,142 +11902,142 @@
         <v>183</v>
       </c>
       <c r="DK23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ23" t="s">
         <v>184</v>
       </c>
-      <c r="DL23" t="s">
-        <v>184</v>
-      </c>
-      <c r="DM23" t="s">
-        <v>184</v>
-      </c>
-      <c r="DN23" t="s">
+      <c r="DR23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY23" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC23" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ23" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER23" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES23" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY23" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ23" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA23" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB23" t="s">
         <v>185</v>
       </c>
-      <c r="DO23" t="s">
+      <c r="FC23" t="s">
         <v>185</v>
       </c>
-      <c r="DP23" t="s">
-        <v>184</v>
-      </c>
-      <c r="DQ23" t="s">
-        <v>186</v>
-      </c>
-      <c r="DR23" t="s">
+      <c r="FD23" t="s">
         <v>185</v>
-      </c>
-      <c r="DS23" t="s">
-        <v>185</v>
-      </c>
-      <c r="DT23" t="s">
-        <v>185</v>
-      </c>
-      <c r="DU23" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV23" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW23" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX23" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY23" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC23" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ23" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER23" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES23" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY23" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ23" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA23" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB23" t="s">
-        <v>190</v>
-      </c>
-      <c r="FC23" t="s">
-        <v>190</v>
-      </c>
-      <c r="FD23" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:160">
@@ -12123,7 +12078,7 @@
         <v>183</v>
       </c>
       <c r="M24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N24" t="s">
         <v>183</v>
@@ -12159,412 +12114,412 @@
         <v>183</v>
       </c>
       <c r="Y24" t="s">
+        <v>183</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AS24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AU24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AY24" t="s">
+        <v>183</v>
+      </c>
+      <c r="AZ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BA24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BB24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BD24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BE24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BF24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BG24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BH24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BJ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BK24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BL24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BM24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BN24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BP24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BQ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BS24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BU24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BV24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BW24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BX24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BY24" t="s">
+        <v>183</v>
+      </c>
+      <c r="BZ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CA24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CC24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CD24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CE24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CF24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CG24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CH24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CI24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CJ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CK24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CL24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CM24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CN24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CO24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CP24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CQ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CR24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CS24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CT24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CU24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CV24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CW24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CX24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CY24" t="s">
+        <v>183</v>
+      </c>
+      <c r="CZ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DA24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DB24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DC24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DD24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DE24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DF24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DG24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DH24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DI24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DJ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DK24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DL24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DM24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DN24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DO24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DP24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DQ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DR24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DS24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DT24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DU24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DW24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DX24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DY24" t="s">
+        <v>183</v>
+      </c>
+      <c r="DZ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EA24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EC24" t="s">
+        <v>183</v>
+      </c>
+      <c r="ED24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EE24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EF24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EG24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EH24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EI24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EJ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EK24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EL24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EM24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EN24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EO24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EP24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EQ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="ER24" t="s">
+        <v>183</v>
+      </c>
+      <c r="ES24" t="s">
+        <v>183</v>
+      </c>
+      <c r="ET24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EU24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EV24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EW24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EX24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EY24" t="s">
+        <v>183</v>
+      </c>
+      <c r="EZ24" t="s">
+        <v>183</v>
+      </c>
+      <c r="FA24" t="s">
+        <v>183</v>
+      </c>
+      <c r="FB24" t="s">
         <v>185</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="FC24" t="s">
         <v>185</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="FD24" t="s">
         <v>185</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>185</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>184</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AO24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AP24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AR24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AS24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AT24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AU24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AV24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AW24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AX24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AY24" t="s">
-        <v>183</v>
-      </c>
-      <c r="AZ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BA24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BB24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BC24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BD24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BE24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BF24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BG24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BH24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BJ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BK24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BL24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BM24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BN24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BO24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BP24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BR24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BS24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BU24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BV24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BW24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BX24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY24" t="s">
-        <v>183</v>
-      </c>
-      <c r="BZ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CA24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CC24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CD24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CE24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CF24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CG24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CH24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CI24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CJ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CK24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CL24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CM24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CN24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CO24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CP24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CQ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CR24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CS24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CT24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CU24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CV24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CW24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CX24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CY24" t="s">
-        <v>183</v>
-      </c>
-      <c r="CZ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DA24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DB24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DC24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DD24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DE24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DF24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DG24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DH24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DI24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DJ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DK24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DL24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DM24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DN24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DO24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DP24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DQ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DR24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DS24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DT24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DU24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DV24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DW24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DY24" t="s">
-        <v>183</v>
-      </c>
-      <c r="DZ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EA24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EB24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EC24" t="s">
-        <v>183</v>
-      </c>
-      <c r="ED24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EE24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EF24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EG24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EH24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EI24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EJ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EK24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EL24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EM24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EN24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EO24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EP24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EQ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="ER24" t="s">
-        <v>183</v>
-      </c>
-      <c r="ES24" t="s">
-        <v>183</v>
-      </c>
-      <c r="ET24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EU24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EV24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EW24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EX24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EY24" t="s">
-        <v>183</v>
-      </c>
-      <c r="EZ24" t="s">
-        <v>183</v>
-      </c>
-      <c r="FA24" t="s">
-        <v>183</v>
-      </c>
-      <c r="FB24" t="s">
-        <v>190</v>
-      </c>
-      <c r="FC24" t="s">
-        <v>188</v>
-      </c>
-      <c r="FD24" t="s">
-        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ToT_tukey_classification_matrix.xlsx
+++ b/outputs/ToT_tukey_classification_matrix.xlsx
@@ -565,7 +565,7 @@
     <t>West Pokot</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
